--- a/Skill AI.xlsx
+++ b/Skill AI.xlsx
@@ -5,17 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Library\Skill-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13F6554-43E8-47A0-9B1C-EE4010D01AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3DA508-E9AB-49C7-9C47-2836F34BB2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thư viện chính" sheetId="1" r:id="rId1"/>
+    <sheet name="Prompt nâng cao" sheetId="2" r:id="rId2"/>
+    <sheet name="Guide" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -72,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8352" uniqueCount="3472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8391" uniqueCount="3507">
   <si>
     <t>Lệnh/Skill</t>
   </si>
@@ -10488,13 +10503,158 @@
   </si>
   <si>
     <t>/educationalcomics [dán bài học cần chuyển thành truyện tranh giáo dục]</t>
+  </si>
+  <si>
+    <t>XÂY DỰNG BẢN KẾ HOẠCH WEBSITE HOÀN CHỈNH</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một chuyên gia chiến lược website cấp cao.
+Lên kế hoạch cho một website dành cho [business type], hướng đến [audience] tại [location].
+Xác định các trang thiết yếu, hệ thống điều hướng, cấu trúc phân cấp trang và hành trình người dùng giúp thúc đẩy [sales/leads/bookings].
+Giữ cấu trúc có tính chiến lược, đơn giản và dễ tiếp cận với người mới.</t>
+  </si>
+  <si>
+    <t>Fullstack
+Front-end</t>
+  </si>
+  <si>
+    <t>THIẾT KẾ TRANG CHỦ THÚC ĐẤY CHUYẾN ĐỐI</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một nhà thiết kế website tập trung vào chuyển đổi.
+Xây dựng cấu trúc trang chủ cho [business type], bao gồm phần mở đầu nổi bật và hấp dẫng lợi ích, dịch vụ, lời chứng thực, câu hỏi thường gặp, các yếu tố tạo niềm tỉn và lời kêu gọi hành động rõ ràng.
+Giải thích mục đích của từng phần và cách phần đó dẫn dắt khách truy cập đến [goal].</t>
+  </si>
+  <si>
+    <t>Front-end</t>
+  </si>
+  <si>
+    <t>VIẾT NỘI DUNG TRANG CHỦ THUYẾT PHỤC</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một chuyên gia viết nội dung quảng cáo hướng đến phản hồi trực tiếp.
+Viết nội dung trang chủ cho [business type], hướng đến [audience].
+Bao gồm tiêu đề mạnh mẽ, tiêu đề phụ bổ trợ, ba lợi ích tập trung vào khách hàng, các nút kêu gọi hành động thuyết phục và phần kết giúp xây dựng niềm tỉn.
+Sử dụng giọng điệu [tone] và loại bỏ những lời lẽ dài dòng không cần thiết.</t>
+  </si>
+  <si>
+    <t>TẠO HỆ THỐNG THIẾT KẾ WEBSITE CAO CẤP</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một nhà thiết kế UI/UX. Tạo bộ nhận diện hình ảnh chỉn chu cho website [business type], bao gồm bảng màu đồng bộ kèm mã HEX, phông chữ tiêu đề và nội dung, kiểu nút bấmg quy tắc khoảng cách và hướng dẫn thiết kế.
+Thể hiện phong cách thẩm mỹ [modern/luxury/minimal], đồng thời bảo đảm người mới có thể dễ dàng triển khai.</t>
+  </si>
+  <si>
+    <t>TẠO MÃ WEBSITE TƯƠNG THÍCH NHIỀU KÍCH THƯỚC MÀN HÌNH</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một lập trình viên giao diện web.
+Xây dựng một trang đích cho [business type] bằng HTML và CSS, có khả năng thích ứng với nhiều kích thước màn hình.
+Bao gồm phần mở đầu nổi bật, dịch vụ, lợi ích, lời chứng thực và lời kêu gọi hành động.
+Sử dụng HTML có ngữ nghĩa, CSS rõ ràng, các thành phần bảo đảm khả năng tiếp cận và cách thiết kế ưu tiên thiết bị di động.
+Cung cấp mã hoàn chỉnh, có thể chỉnh sửa, kèm hướng dẫn thiết lập ngắn gọn.</t>
+  </si>
+  <si>
+    <t>TẠO TRANG DỊCH VỤ GIÚP BÁN HÀNG</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một chuyên gia chiến lược nội dung website.
+Viết trang dịch vụ cho [business type], cung cấp [service 1], [service 2] và [service 3].
+Với mỗi dịch vụ, hãy đưa ra tiêu đề rõ ràng, mô tả ngắn, khách hàng lý tưởng, kết quả chính và lời kêu gọi hành động.
+Nhấn mạnh kết quả khách hàng nhận được, tính dễ đọc và sự tin cậy.</t>
+  </si>
+  <si>
+    <t>Front-end
+Business Analysis</t>
+  </si>
+  <si>
+    <t>VIẾT TRANG GIỚI THIỆU CHÂN THỰC</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một người kể chuyện thương hiệu.
+Viết trang Giới thiệu cho [business/person/brand] nhằm xây dựng niềm tin.
+Bao gồm câu chuyện khởi nguồn, Sứ mệnh, giá trị cốt lõi, thế mạnh riêng và lý do khách hàng nên lựa chọn doanh nghiệp, cá nhân hoặc thương hiệu này.
+Sử dụng giọng điệu [friendly/professional/warm], tạo cảm giác gần gũi như con người, đáng tin cậy và dễ đồng cảm.</t>
+  </si>
+  <si>
+    <t>Front-end
+Personal</t>
+  </si>
+  <si>
+    <t>TỐI ƯU NỘI DUNG WEBSITE CHO SEO</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một chuyên gia SEO.
+Tạo nội dung được tối ưu cho [page type], nhắm đến [keyword/topic] và [audience].
+Bao gồm tiêu đề hấp dẫng hệ thống đề mục có cấu trúc, các cụm từ tìm kiếm liên quan, các đoạn văn dễ đọc và phần mô tả meta thuyết phục.
+Đáp ứng ý định tìm kiếm một cách tự nhiên, không nhồi nhét từ khóa.</t>
+  </si>
+  <si>
+    <t>Front-end
+SEO</t>
+  </si>
+  <si>
+    <t>ĐÁNH GIÁ VÀ CẢI THIỆN TRẢI NGHIỆM NGƯỜI DÙNG WEBSITE</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một chuyên gia UX,
+Đánh giá website của tôi tại [URL] hoặc phân tích ý tuong website sau: [description].
+Xác định các vấn đề về điều hướng, bố cục, phân cấp thị giác, tính dễ đọc, lời kêu gọi hành động,khả năng tiếp cận và tính dễ sử dụng trên thiết bị di động.
+Xếp hạng các đề xuất theo mức độ tác động và đưa ra cách khắc phục thực tế cho từng vấn đề.</t>
+  </si>
+  <si>
+    <t>Front-end
+UI/UX</t>
+  </si>
+  <si>
+    <t>GỠ LỖI VÀ TỐI ƯU MÃ WEBSITE</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai một lập trình viên giao diện web cấp cao.
+Rà soát đoạn mã sau: [paste code].
+Xác định và sửa lỗi, cải thiện khả năng thích ứng với các kích thước màn hình, khả năng tiếp cận, hiệu suất và cấu trúc mã.
+Giữ nguyên các chức năng hiện có, giải thích ngắn gọn những thay đổi quan trọng và trả về toàn bộ mã đã sửa.</t>
+  </si>
+  <si>
+    <t>Front-end
+Fullstack
+Debugger</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Hãy đóng vai là một gia sư tiếng Anh giao tiếp hàng đầu chuyên hỗ trợ người Việt nâng cao kỹ năng nói. Trước hết, hãy đánh giá trình độ hiện tại của tôi, sau đó cung cấp các mẫu câu giao tiếp thực tế cùng bài tập hội thoại theo tình huống. 
+Trong quá trình luyện tập, hãy kịp thời sửa lỗi sai và tối ưu cách diễn đạt cho tôi.</t>
+  </si>
+  <si>
+    <t>Learn
+Language</t>
+  </si>
+  <si>
+    <t>GIA SƯ TIẾNG ANH</t>
+  </si>
+  <si>
+    <t>GEN ẢNH (KHÔNG BỊ CẢM GIÁC QUÁ AI)</t>
+  </si>
+  <si>
+    <t>Phóng cách ảnh chụp thật, ống kính 50mm, khẩu độ F1.8, nền mờ nhẹ
+Ánh sáng tự nhiên ban ngày, câng bằng trắng khoảng 5500K, không ám vàng, không lệch màu.
+Xóa hết chi tiết thừa, bóng đổ mềm, tự nhiên, màu điềm đạm, không quá rực.</t>
+  </si>
+  <si>
+    <t>Generative
+Image</t>
+  </si>
+  <si>
+    <t>Prompt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10516,6 +10676,37 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -10556,7 +10747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -10565,21 +10756,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <strike val="0"/>
@@ -10671,6 +10868,96 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -10685,17 +10972,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LibraryFinalChecked" displayName="LibraryFinalChecked" ref="A1:F1392" headerRowDxfId="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LibraryFinalChecked" displayName="LibraryFinalChecked" ref="A1:F1392" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:F1392" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Lệnh/Skill" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Mô tả" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dùng khi" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Cách dùng" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Category" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lĩnh vực" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Lệnh/Skill" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Mô tả" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dùng khi" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Cách dùng" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Category" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lĩnh vực" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1E52C82B-7DD8-4178-81AB-D08F02FA6623}" name="Table1" displayName="Table1" ref="A1:C39" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:C39" xr:uid="{1E52C82B-7DD8-4178-81AB-D08F02FA6623}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{60E97527-7C55-40FE-BA41-EC84ADA85E00}" name="Title" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{412C4265-ED16-402D-874B-1275C1FD496A}" name="Prompt" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{16B39B39-946B-4D90-BAE1-E8F18310F6F0}" name="Category" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -38842,4 +39141,304 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55034B81-2ED1-4830-B0D8-B48C8FAAA169}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="80.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="115.5703125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>3499</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>3472</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3473</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>3475</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3478</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>3482</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>3483</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>3487</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3489</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>3491</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>3493</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>3496</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>3503</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938DE888-BBF4-41AE-B7BC-BFFEE5D4768C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>